--- a/engine/publish_queue/SWDY/SWDY_Valuation_Model_09092026_public.xlsx
+++ b/engine/publish_queue/SWDY/SWDY_Valuation_Model_09092026_public.xlsx
@@ -2560,19 +2560,19 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>54.89390300698878</v>
+        <v>48.0507329597046</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>56.76608049282878</v>
+        <v>49.70216467416559</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>58.9328825766538</v>
+        <v>51.61377072512412</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>61.49018601091854</v>
+        <v>53.8702170590966</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>64.58052940682644</v>
+        <v>56.59737534073271</v>
       </c>
     </row>
     <row r="7">
@@ -2582,19 +2582,19 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>49.59394363429544</v>
+        <v>43.38965839771769</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>50.95326657112403</v>
+        <v>44.58953433723649</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>52.49104063008191</v>
+        <v>45.94722493645097</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>54.25965459765457</v>
+        <v>47.50906063258347</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>56.33422840926579</v>
+        <v>49.34147433400587</v>
       </c>
     </row>
     <row r="8">
@@ -2604,19 +2604,19 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>45.05103667309857</v>
+        <v>39.39440569105454</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>46.03042217002906</v>
+        <v>40.25970494315277</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>47.11281563256473</v>
+        <v>41.21632469837968</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>48.32576211063959</v>
+        <v>42.28868469751839</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>49.7075887045515</v>
+        <v>43.51076338157681</v>
       </c>
     </row>
     <row r="9">
@@ -2626,19 +2626,19 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>41.11553668357441</v>
+        <v>35.93336189108932</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>41.8093978775642</v>
+        <v>36.54718264711511</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>42.55648627630665</v>
+        <v>37.20843070440687</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>43.36987034045674</v>
+        <v>37.92875051852907</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>44.26727799429032</v>
+        <v>38.72393829011554</v>
       </c>
     </row>
     <row r="10">
@@ -2648,19 +2648,19 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>37.67472174247933</v>
+        <v>32.90738826514143</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>38.15151148948571</v>
+        <v>33.32998437664673</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>38.648345329237</v>
+        <v>33.77073485461407</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>39.16977223986016</v>
+        <v>34.23375980649833</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>39.72183036633324</v>
+        <v>34.72452811024157</v>
       </c>
     </row>
     <row r="12">
@@ -2705,19 +2705,19 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>68.64247049591957</v>
+        <v>60.17049350743897</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>66.57546829677946</v>
+        <v>58.35223880309312</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>64.58052940682644</v>
+        <v>56.59737534073271</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>62.65451643723234</v>
+        <v>54.90314327729129</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>60.79445670792633</v>
+        <v>53.26692765802384</v>
       </c>
     </row>
     <row r="15">
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>59.93237666911776</v>
+        <v>52.50650406475745</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>58.10144964510826</v>
+        <v>50.89597043113798</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>56.33422840926579</v>
+        <v>49.34147433400587</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>54.62794387184755</v>
+        <v>47.84057999237388</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>52.9799721331991</v>
+        <v>46.39097933936378</v>
       </c>
     </row>
     <row r="16">
@@ -2749,19 +2749,19 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>52.93321441251824</v>
+        <v>46.34801613119999</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>51.2919036374145</v>
+        <v>44.90432296618077</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>49.7075887045515</v>
+        <v>43.51076338157681</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>48.17779610598239</v>
+        <v>42.16516167246377</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>46.70018186414503</v>
+        <v>40.86545606942517</v>
       </c>
     </row>
     <row r="17">
@@ -2771,19 +2771,19 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>47.18722756407969</v>
+        <v>41.29223410819131</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>45.70150653374164</v>
+        <v>39.98544052927011</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>44.26727799429032</v>
+        <v>38.72393829011554</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>42.88231076920474</v>
+        <v>37.50576490546236</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>41.54449037834811</v>
+        <v>36.3290605333606</v>
       </c>
     </row>
     <row r="18">
@@ -2793,19 +2793,19 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>42.38652255248041</v>
+        <v>37.06823178367044</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>41.03072689368742</v>
+        <v>35.87575503510264</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>39.72183036633324</v>
+        <v>34.72452811024157</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>38.45780396819539</v>
+        <v>33.61276640826723</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>37.23672469018629</v>
+        <v>32.53877855437916</v>
       </c>
     </row>
     <row r="20">
@@ -2836,23 +2836,23 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Beta  (0.60 / 0.80 / 1.23 / 1.15 / 1.30)</t>
+          <t>Beta  (0.60 / 0.80 / 1.15 / 1.23 / 1.30)</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>94.46647146810956</v>
+        <v>82.89233633171949</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>75.25828072607085</v>
+        <v>65.99151475122238</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>49.70341773987482</v>
+        <v>46.59451573941893</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>53.21252849781632</v>
+        <v>43.50709365611225</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>46.50262521769896</v>
+        <v>40.69096331071587</v>
       </c>
       <c r="H22" s="16">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
@@ -2996,19 +2996,19 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>45.05103667309857</v>
+        <v>39.39440569105454</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>46.03042217002906</v>
+        <v>40.25970494315277</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>47.11281563256473</v>
+        <v>41.21632469837968</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>48.32576211063959</v>
+        <v>42.28868469751839</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>49.7075887045515</v>
+        <v>43.51076338157681</v>
       </c>
       <c r="H28" s="16">
         <f>MAX(B28:F28)-MIN(B28:F28)</f>
